--- a/xlsx/data.xlsx
+++ b/xlsx/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tom/Developer/PKMN_G1/pokeyellowCHS/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A1A961-5747-A242-B917-91572CA94646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC889D0-51EE-AD4E-B008-72558DB25948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14120" yWindow="760" windowWidth="20440" windowHeight="20480" activeTab="6" xr2:uid="{5D9A02DE-DD85-974B-B8A1-A92382739B9C}"/>
+    <workbookView xWindow="10200" yWindow="760" windowWidth="20440" windowHeight="20420" activeTab="6" xr2:uid="{5D9A02DE-DD85-974B-B8A1-A92382739B9C}"/>
   </bookViews>
   <sheets>
     <sheet name="PM" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3088" uniqueCount="2207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3088" uniqueCount="2208">
   <si>
     <t>data/pokemon/names.asm</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7615,10 +7615,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>彩色@</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Makefile</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7644,6 +7640,14 @@
   </si>
   <si>
     <t xml:space="preserve"> 第   次 登入名人堂@</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日版@</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美版@</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -16662,7 +16666,7 @@
         <v>1147</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="E39" t="s">
         <v>1285</v>
@@ -16817,7 +16821,7 @@
         <v>2180</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>2199</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -16825,7 +16829,7 @@
         <v>2181</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>2183</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -30490,7 +30494,7 @@
         <v>1495</v>
       </c>
       <c r="C232" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -31797,23 +31801,23 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="B20" s="12" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>2201</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>2202</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="B21" s="12" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>2203</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>2204</v>
       </c>
     </row>
     <row r="22" spans="1:4">
